--- a/activity_protocol.xlsx
+++ b/activity_protocol.xlsx
@@ -461,7 +461,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -550,7 +550,7 @@
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">SUM(D2:D10)</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
